--- a/SAA Biosci 50 BOM_09.06.25.xlsx
+++ b/SAA Biosci 50 BOM_09.06.25.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B8C16115-2024-42D6-B50A-B326406F7ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86ED4A1D-6EED-4D67-A614-0AEEDDB56581}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902A5E5C-35AD-4ABD-8AE1-B6FEE193F92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="187" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="187" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_SAA" sheetId="1" r:id="rId1"/>
@@ -2102,6 +2102,30 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2125,30 +2149,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2467,35 +2467,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J276"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="94.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="42.88671875" style="45" customWidth="1"/>
-    <col min="9" max="9" width="29.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="10.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="94.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="42.85546875" style="45" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="73" t="s">
         <v>455</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="51"/>
       <c r="I1" s="51"/>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -2536,12 +2536,12 @@
       <c r="F3" s="12"/>
       <c r="G3" s="56"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="65" t="s">
         <v>483</v>
       </c>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -2561,13 +2561,13 @@
       <c r="G4" s="57">
         <v>1</v>
       </c>
-      <c r="H4" s="74" t="s">
+      <c r="H4" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="73"/>
+      <c r="I4" s="65"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" ref="A5:A18" si="0">A4+1</f>
         <v>2</v>
@@ -2588,11 +2588,11 @@
       <c r="G5" s="57">
         <v>1</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="73"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="65"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2613,11 +2613,11 @@
       <c r="G6" s="57">
         <v>1</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="73"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="65"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2638,11 +2638,11 @@
       <c r="G7" s="57">
         <v>1</v>
       </c>
-      <c r="H7" s="75"/>
-      <c r="I7" s="73"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="65"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2663,11 +2663,11 @@
       <c r="G8" s="57">
         <v>1</v>
       </c>
-      <c r="H8" s="75"/>
-      <c r="I8" s="73"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="65"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2688,11 +2688,11 @@
       <c r="G9" s="57">
         <v>1</v>
       </c>
-      <c r="H9" s="75"/>
-      <c r="I9" s="73"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="65"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2713,11 +2713,11 @@
       <c r="G10" s="57">
         <v>1</v>
       </c>
-      <c r="H10" s="75"/>
-      <c r="I10" s="73"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="65"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2738,11 +2738,11 @@
       <c r="G11" s="57">
         <v>1</v>
       </c>
-      <c r="H11" s="75"/>
-      <c r="I11" s="73"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="65"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2763,11 +2763,11 @@
       <c r="G12" s="57">
         <v>1</v>
       </c>
-      <c r="H12" s="75"/>
-      <c r="I12" s="73"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="65"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2788,11 +2788,11 @@
       <c r="G13" s="57">
         <v>1</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="73"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="65"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2813,11 +2813,11 @@
       <c r="G14" s="57">
         <v>1</v>
       </c>
-      <c r="H14" s="75"/>
-      <c r="I14" s="73"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="65"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2838,11 +2838,11 @@
       <c r="G15" s="57">
         <v>1</v>
       </c>
-      <c r="H15" s="75"/>
-      <c r="I15" s="73"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="65"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2863,11 +2863,11 @@
       <c r="G16" s="57">
         <v>1</v>
       </c>
-      <c r="H16" s="75"/>
-      <c r="I16" s="73"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="65"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2888,11 +2888,11 @@
       <c r="G17" s="57">
         <v>1</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="73"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="65"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2913,11 +2913,11 @@
       <c r="G18" s="57">
         <v>1</v>
       </c>
-      <c r="H18" s="76"/>
-      <c r="I18" s="73"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="65"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -2938,10 +2938,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="34"/>
-      <c r="I19" s="73"/>
+      <c r="I19" s="65"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="4"/>
       <c r="C20" s="6"/>
@@ -2953,7 +2953,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>40</v>
       </c>
@@ -2967,7 +2967,7 @@
       <c r="I21" s="11"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>1</v>
       </c>
@@ -2988,12 +2988,12 @@
         <v>1</v>
       </c>
       <c r="H22" s="20"/>
-      <c r="I22" s="77" t="s">
+      <c r="I22" s="69" t="s">
         <v>513</v>
       </c>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>2</v>
       </c>
@@ -3014,10 +3014,10 @@
         <v>1</v>
       </c>
       <c r="H23" s="20"/>
-      <c r="I23" s="78"/>
+      <c r="I23" s="70"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>3</v>
       </c>
@@ -3038,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="20"/>
-      <c r="I24" s="78"/>
+      <c r="I24" s="70"/>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -3062,10 +3062,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="20"/>
-      <c r="I25" s="78"/>
+      <c r="I25" s="70"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>5</v>
       </c>
@@ -3086,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="20"/>
-      <c r="I26" s="78"/>
+      <c r="I26" s="70"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>6</v>
       </c>
@@ -3110,10 +3110,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="20"/>
-      <c r="I27" s="78"/>
+      <c r="I27" s="70"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>7</v>
       </c>
@@ -3134,10 +3134,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="20"/>
-      <c r="I28" s="78"/>
+      <c r="I28" s="70"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>8</v>
       </c>
@@ -3158,10 +3158,10 @@
         <v>1</v>
       </c>
       <c r="H29" s="20"/>
-      <c r="I29" s="78"/>
+      <c r="I29" s="70"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>9</v>
       </c>
@@ -3182,10 +3182,10 @@
         <v>1</v>
       </c>
       <c r="H30" s="20"/>
-      <c r="I30" s="79"/>
+      <c r="I30" s="71"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>10</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="9"/>
@@ -3221,7 +3221,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>61</v>
       </c>
@@ -3235,7 +3235,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1</v>
       </c>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>2</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>3</v>
       </c>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>4</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="I37" s="9"/>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>5</v>
       </c>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="J38" s="5"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>6</v>
       </c>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="1:10" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>7</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>8</v>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>9</v>
       </c>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>10</v>
       </c>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -3521,7 +3521,7 @@
       <c r="I44" s="9"/>
       <c r="J44" s="5"/>
     </row>
-    <row r="45" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>75</v>
       </c>
@@ -3535,7 +3535,7 @@
       <c r="I45" s="11"/>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="35">
         <v>1</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f>A46+1</f>
         <v>2</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>3</v>
       </c>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>4</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>78</v>
       </c>
@@ -3676,7 +3676,7 @@
       <c r="I51" s="11"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="15" t="s">
         <v>302</v>
@@ -3696,7 +3696,7 @@
       <c r="I52" s="11"/>
       <c r="J52" s="12"/>
     </row>
-    <row r="53" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="15" t="s">
         <v>303</v>
@@ -3716,7 +3716,7 @@
       <c r="G53" s="59">
         <v>1</v>
       </c>
-      <c r="H53" s="72" t="s">
+      <c r="H53" s="80" t="s">
         <v>81</v>
       </c>
       <c r="I53" s="38" t="s">
@@ -3726,7 +3726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="15" t="s">
         <v>304</v>
@@ -3746,7 +3746,7 @@
       <c r="G54" s="59">
         <v>1</v>
       </c>
-      <c r="H54" s="72"/>
+      <c r="H54" s="80"/>
       <c r="I54" s="38" t="s">
         <v>483</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="15" t="s">
         <v>305</v>
@@ -3774,7 +3774,7 @@
       <c r="G55" s="59">
         <v>1</v>
       </c>
-      <c r="H55" s="72"/>
+      <c r="H55" s="80"/>
       <c r="I55" s="38" t="s">
         <v>483</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="15" t="s">
         <v>306</v>
@@ -3802,7 +3802,7 @@
       <c r="G56" s="59">
         <v>1</v>
       </c>
-      <c r="H56" s="72"/>
+      <c r="H56" s="80"/>
       <c r="I56" s="38" t="s">
         <v>483</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="15" t="s">
         <v>307</v>
@@ -3840,7 +3840,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="10" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" s="10" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="15" t="s">
         <v>308</v>
@@ -3870,7 +3870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" s="10" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="15" t="s">
         <v>309</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="15" t="s">
         <v>310</v>
@@ -3930,7 +3930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="15" t="s">
         <v>311</v>
@@ -3960,7 +3960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="35"/>
       <c r="B62" s="35" t="s">
         <v>312</v>
@@ -3990,7 +3990,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="35"/>
       <c r="B63" s="35" t="s">
         <v>313</v>
@@ -4020,7 +4020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="15" t="s">
         <v>317</v>
@@ -4046,7 +4046,7 @@
       <c r="I64" s="11"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -4058,7 +4058,7 @@
       <c r="I65" s="11"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="15" t="s">
         <v>314</v>
@@ -4078,7 +4078,7 @@
       <c r="I66" s="11"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="15" t="s">
         <v>315</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35" t="s">
         <v>316</v>
@@ -4138,7 +4138,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
       <c r="B69" s="15" t="s">
         <v>318</v>
@@ -4168,7 +4168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -4180,7 +4180,7 @@
       <c r="I70" s="11"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
       <c r="B71" s="15" t="s">
         <v>319</v>
@@ -4200,7 +4200,7 @@
       <c r="I71" s="11"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
       <c r="B72" s="15" t="s">
         <v>320</v>
@@ -4230,7 +4230,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
       <c r="B73" s="15" t="s">
         <v>321</v>
@@ -4260,7 +4260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
       <c r="B74" s="15" t="s">
         <v>322</v>
@@ -4290,7 +4290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -4302,7 +4302,7 @@
       <c r="I75" s="11"/>
       <c r="J75" s="12"/>
     </row>
-    <row r="76" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
       <c r="B76" s="15" t="s">
         <v>323</v>
@@ -4322,7 +4322,7 @@
       <c r="I76" s="11"/>
       <c r="J76" s="12"/>
     </row>
-    <row r="77" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="35"/>
       <c r="B77" s="35" t="s">
         <v>324</v>
@@ -4352,7 +4352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="10" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
       <c r="B78" s="15" t="s">
         <v>325</v>
@@ -4382,7 +4382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
       <c r="B79" s="15" t="s">
         <v>326</v>
@@ -4412,7 +4412,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
       <c r="B80" s="15" t="s">
         <v>327</v>
@@ -4442,7 +4442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
       <c r="B81" s="15" t="s">
         <v>328</v>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
       <c r="B82" s="15" t="s">
         <v>329</v>
@@ -4502,7 +4502,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
       <c r="B83" s="15" t="s">
         <v>520</v>
@@ -4530,7 +4530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="35" t="s">
         <v>523</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="J84" s="5"/>
     </row>
-    <row r="85" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -4568,7 +4568,7 @@
       <c r="I85" s="11"/>
       <c r="J85" s="12"/>
     </row>
-    <row r="86" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
       <c r="B86" s="15" t="s">
         <v>330</v>
@@ -4588,7 +4588,7 @@
       <c r="I86" s="11"/>
       <c r="J86" s="12"/>
     </row>
-    <row r="87" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
       <c r="B87" s="15" t="s">
         <v>331</v>
@@ -4618,7 +4618,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
       <c r="B88" s="15" t="s">
         <v>332</v>
@@ -4648,7 +4648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
       <c r="B89" s="15" t="s">
         <v>333</v>
@@ -4678,7 +4678,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
       <c r="B90" s="15" t="s">
         <v>334</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="J90" s="12"/>
     </row>
-    <row r="91" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
       <c r="B91" s="15" t="s">
         <v>335</v>
@@ -4736,7 +4736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
       <c r="B92" s="15" t="s">
         <v>336</v>
@@ -4766,7 +4766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
@@ -4778,7 +4778,7 @@
       <c r="I93" s="11"/>
       <c r="J93" s="12"/>
     </row>
-    <row r="94" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
       <c r="B94" s="15" t="s">
         <v>337</v>
@@ -4800,7 +4800,7 @@
       <c r="I94" s="11"/>
       <c r="J94" s="12"/>
     </row>
-    <row r="95" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
       <c r="B95" s="15" t="s">
         <v>338</v>
@@ -4830,7 +4830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="35" t="s">
         <v>339</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="J96" s="5"/>
     </row>
-    <row r="97" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="18"/>
       <c r="C97" s="15"/>
@@ -4870,7 +4870,7 @@
       <c r="I97" s="11"/>
       <c r="J97" s="12"/>
     </row>
-    <row r="98" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
       <c r="B98" s="15" t="s">
         <v>340</v>
@@ -4890,7 +4890,7 @@
       <c r="I98" s="11"/>
       <c r="J98" s="12"/>
     </row>
-    <row r="99" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
       <c r="B99" s="15" t="s">
         <v>341</v>
@@ -4920,7 +4920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="15" t="s">
         <v>342</v>
@@ -4950,7 +4950,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
       <c r="B101" s="15" t="s">
         <v>343</v>
@@ -4980,7 +4980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
       <c r="B102" s="15"/>
       <c r="C102" s="18"/>
@@ -4992,7 +4992,7 @@
       <c r="I102" s="11"/>
       <c r="J102" s="12"/>
     </row>
-    <row r="103" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="15" t="s">
         <v>344</v>
@@ -5010,7 +5010,7 @@
       <c r="I103" s="11"/>
       <c r="J103" s="12"/>
     </row>
-    <row r="104" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
       <c r="B104" s="15" t="s">
         <v>345</v>
@@ -5040,7 +5040,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="105" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
       <c r="B105" s="15" t="s">
         <v>346</v>
@@ -5070,7 +5070,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="35" t="s">
         <v>347</v>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J106" s="5"/>
     </row>
-    <row r="107" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="35" t="s">
         <v>348</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="J107" s="5"/>
     </row>
-    <row r="108" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
       <c r="B108" s="18"/>
       <c r="C108" s="15"/>
@@ -5138,7 +5138,7 @@
       <c r="I108" s="11"/>
       <c r="J108" s="12"/>
     </row>
-    <row r="109" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
         <v>126</v>
       </c>
@@ -5152,7 +5152,7 @@
       <c r="I109" s="17"/>
       <c r="J109" s="15"/>
     </row>
-    <row r="110" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="35">
         <v>1</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>2</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>3</v>
       </c>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="J112" s="5"/>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>4</v>
       </c>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="J113" s="5"/>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>5</v>
       </c>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="J114" s="5"/>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>6</v>
       </c>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="J115" s="5"/>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>7</v>
       </c>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="J116" s="5"/>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>8</v>
       </c>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="J117" s="5"/>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>9</v>
       </c>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="J118" s="5"/>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>10</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="32.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>11</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>12</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="35">
         <v>13</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>14</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>15</v>
       </c>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="J124" s="5"/>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>16</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>17</v>
       </c>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="J126" s="5"/>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>18</v>
       </c>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="J127" s="5"/>
     </row>
-    <row r="128" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="35">
         <v>19</v>
       </c>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="J128" s="5"/>
     </row>
-    <row r="129" spans="1:10" s="16" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" s="16" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>20</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>21</v>
       </c>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="J130" s="5"/>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>22</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="33"/>
@@ -5800,7 +5800,7 @@
       <c r="I132" s="9"/>
       <c r="J132" s="5"/>
     </row>
-    <row r="133" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>157</v>
       </c>
@@ -5814,7 +5814,7 @@
       <c r="I133" s="11"/>
       <c r="J133" s="12"/>
     </row>
-    <row r="134" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>1</v>
       </c>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="J134" s="5"/>
     </row>
-    <row r="135" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>2</v>
       </c>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="J135" s="5"/>
     </row>
-    <row r="136" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>3</v>
       </c>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="J136" s="5"/>
     </row>
-    <row r="137" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>4</v>
       </c>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="J137" s="5"/>
     </row>
-    <row r="138" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>5</v>
       </c>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="J138" s="5"/>
     </row>
-    <row r="139" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>6</v>
       </c>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="J139" s="5"/>
     </row>
-    <row r="140" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>7</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="J140" s="5"/>
     </row>
-    <row r="141" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>8</v>
       </c>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="J141" s="5"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="35"/>
       <c r="B142" s="35"/>
       <c r="C142" s="35"/>
@@ -6034,7 +6034,7 @@
       <c r="I142" s="49"/>
       <c r="J142" s="5"/>
     </row>
-    <row r="143" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>159</v>
       </c>
@@ -6050,7 +6050,7 @@
       <c r="I143" s="17"/>
       <c r="J143" s="15"/>
     </row>
-    <row r="144" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="27">
         <v>1</v>
       </c>
@@ -6070,15 +6070,15 @@
       <c r="G144" s="61">
         <v>2</v>
       </c>
-      <c r="H144" s="68" t="s">
+      <c r="H144" s="76" t="s">
         <v>495</v>
       </c>
-      <c r="I144" s="80" t="s">
+      <c r="I144" s="72" t="s">
         <v>482</v>
       </c>
       <c r="J144" s="5"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="27">
         <v>2</v>
       </c>
@@ -6098,11 +6098,11 @@
       <c r="G145" s="61">
         <v>4</v>
       </c>
-      <c r="H145" s="68"/>
-      <c r="I145" s="80"/>
+      <c r="H145" s="76"/>
+      <c r="I145" s="72"/>
       <c r="J145" s="5"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="27">
         <v>3</v>
       </c>
@@ -6122,11 +6122,11 @@
       <c r="G146" s="61">
         <v>47</v>
       </c>
-      <c r="H146" s="68"/>
-      <c r="I146" s="80"/>
+      <c r="H146" s="76"/>
+      <c r="I146" s="72"/>
       <c r="J146" s="5"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="27">
         <v>4</v>
       </c>
@@ -6146,11 +6146,11 @@
       <c r="G147" s="61">
         <v>6</v>
       </c>
-      <c r="H147" s="68"/>
-      <c r="I147" s="80"/>
+      <c r="H147" s="76"/>
+      <c r="I147" s="72"/>
       <c r="J147" s="5"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="27">
         <v>5</v>
       </c>
@@ -6170,11 +6170,11 @@
       <c r="G148" s="61">
         <v>35</v>
       </c>
-      <c r="H148" s="68"/>
-      <c r="I148" s="80"/>
+      <c r="H148" s="76"/>
+      <c r="I148" s="72"/>
       <c r="J148" s="5"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="27">
         <v>6</v>
       </c>
@@ -6194,11 +6194,11 @@
       <c r="G149" s="61">
         <v>6</v>
       </c>
-      <c r="H149" s="68"/>
-      <c r="I149" s="80"/>
+      <c r="H149" s="76"/>
+      <c r="I149" s="72"/>
       <c r="J149" s="5"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="27">
         <v>7</v>
       </c>
@@ -6218,11 +6218,11 @@
       <c r="G150" s="61">
         <v>2</v>
       </c>
-      <c r="H150" s="68"/>
-      <c r="I150" s="80"/>
+      <c r="H150" s="76"/>
+      <c r="I150" s="72"/>
       <c r="J150" s="5"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="27">
         <v>8</v>
       </c>
@@ -6242,11 +6242,11 @@
       <c r="G151" s="61">
         <v>2</v>
       </c>
-      <c r="H151" s="68"/>
-      <c r="I151" s="80"/>
+      <c r="H151" s="76"/>
+      <c r="I151" s="72"/>
       <c r="J151" s="5"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="27">
         <v>9</v>
       </c>
@@ -6266,11 +6266,11 @@
       <c r="G152" s="61">
         <v>2</v>
       </c>
-      <c r="H152" s="68"/>
-      <c r="I152" s="80"/>
+      <c r="H152" s="76"/>
+      <c r="I152" s="72"/>
       <c r="J152" s="5"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="27">
         <v>10</v>
       </c>
@@ -6290,11 +6290,11 @@
       <c r="G153" s="61">
         <v>2</v>
       </c>
-      <c r="H153" s="68"/>
-      <c r="I153" s="80"/>
+      <c r="H153" s="76"/>
+      <c r="I153" s="72"/>
       <c r="J153" s="5"/>
     </row>
-    <row r="154" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="27">
         <v>11</v>
       </c>
@@ -6314,11 +6314,11 @@
       <c r="G154" s="61">
         <v>4</v>
       </c>
-      <c r="H154" s="68"/>
-      <c r="I154" s="80"/>
+      <c r="H154" s="76"/>
+      <c r="I154" s="72"/>
       <c r="J154" s="5"/>
     </row>
-    <row r="155" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="27">
         <v>12</v>
       </c>
@@ -6338,11 +6338,11 @@
       <c r="G155" s="61">
         <v>5</v>
       </c>
-      <c r="H155" s="68"/>
-      <c r="I155" s="80"/>
+      <c r="H155" s="76"/>
+      <c r="I155" s="72"/>
       <c r="J155" s="5"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="27">
         <v>13</v>
       </c>
@@ -6362,11 +6362,11 @@
       <c r="G156" s="61">
         <v>20</v>
       </c>
-      <c r="H156" s="68"/>
-      <c r="I156" s="80"/>
+      <c r="H156" s="76"/>
+      <c r="I156" s="72"/>
       <c r="J156" s="5"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="27">
         <v>14</v>
       </c>
@@ -6386,11 +6386,11 @@
       <c r="G157" s="61">
         <v>10</v>
       </c>
-      <c r="H157" s="68"/>
-      <c r="I157" s="80"/>
+      <c r="H157" s="76"/>
+      <c r="I157" s="72"/>
       <c r="J157" s="5"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="27">
         <v>15</v>
       </c>
@@ -6410,11 +6410,11 @@
       <c r="G158" s="61">
         <v>4</v>
       </c>
-      <c r="H158" s="68"/>
-      <c r="I158" s="80"/>
+      <c r="H158" s="76"/>
+      <c r="I158" s="72"/>
       <c r="J158" s="5"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="41">
         <v>16</v>
       </c>
@@ -6434,11 +6434,11 @@
       <c r="G159" s="60">
         <v>4</v>
       </c>
-      <c r="H159" s="68"/>
-      <c r="I159" s="80"/>
+      <c r="H159" s="76"/>
+      <c r="I159" s="72"/>
       <c r="J159" s="5"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="27">
         <v>17</v>
       </c>
@@ -6458,11 +6458,11 @@
       <c r="G160" s="61">
         <v>6</v>
       </c>
-      <c r="H160" s="68"/>
-      <c r="I160" s="80"/>
+      <c r="H160" s="76"/>
+      <c r="I160" s="72"/>
       <c r="J160" s="5"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="27">
         <v>18</v>
       </c>
@@ -6482,11 +6482,11 @@
       <c r="G161" s="61">
         <v>4</v>
       </c>
-      <c r="H161" s="68"/>
-      <c r="I161" s="80"/>
+      <c r="H161" s="76"/>
+      <c r="I161" s="72"/>
       <c r="J161" s="5"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="27">
         <v>19</v>
       </c>
@@ -6506,11 +6506,11 @@
       <c r="G162" s="61">
         <v>4</v>
       </c>
-      <c r="H162" s="68"/>
-      <c r="I162" s="80"/>
+      <c r="H162" s="76"/>
+      <c r="I162" s="72"/>
       <c r="J162" s="5"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="27">
         <v>20</v>
       </c>
@@ -6530,11 +6530,11 @@
       <c r="G163" s="61">
         <v>5</v>
       </c>
-      <c r="H163" s="68"/>
-      <c r="I163" s="80"/>
+      <c r="H163" s="76"/>
+      <c r="I163" s="72"/>
       <c r="J163" s="5"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="27">
         <v>21</v>
       </c>
@@ -6554,11 +6554,11 @@
       <c r="G164" s="61">
         <v>4</v>
       </c>
-      <c r="H164" s="68"/>
-      <c r="I164" s="80"/>
+      <c r="H164" s="76"/>
+      <c r="I164" s="72"/>
       <c r="J164" s="5"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="27">
         <v>22</v>
       </c>
@@ -6578,11 +6578,11 @@
       <c r="G165" s="61">
         <v>4</v>
       </c>
-      <c r="H165" s="68"/>
-      <c r="I165" s="80"/>
+      <c r="H165" s="76"/>
+      <c r="I165" s="72"/>
       <c r="J165" s="5"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="27">
         <v>23</v>
       </c>
@@ -6602,11 +6602,11 @@
       <c r="G166" s="61">
         <v>2</v>
       </c>
-      <c r="H166" s="68"/>
-      <c r="I166" s="80"/>
+      <c r="H166" s="76"/>
+      <c r="I166" s="72"/>
       <c r="J166" s="5"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="27">
         <v>24</v>
       </c>
@@ -6626,11 +6626,11 @@
       <c r="G167" s="61">
         <v>8</v>
       </c>
-      <c r="H167" s="68"/>
-      <c r="I167" s="80"/>
+      <c r="H167" s="76"/>
+      <c r="I167" s="72"/>
       <c r="J167" s="5"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="27">
         <v>25</v>
       </c>
@@ -6650,11 +6650,11 @@
       <c r="G168" s="61">
         <v>13</v>
       </c>
-      <c r="H168" s="68"/>
-      <c r="I168" s="80"/>
+      <c r="H168" s="76"/>
+      <c r="I168" s="72"/>
       <c r="J168" s="5"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="27">
         <v>26</v>
       </c>
@@ -6674,11 +6674,11 @@
       <c r="G169" s="61">
         <v>1</v>
       </c>
-      <c r="H169" s="68"/>
-      <c r="I169" s="80"/>
+      <c r="H169" s="76"/>
+      <c r="I169" s="72"/>
       <c r="J169" s="5"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="41">
         <v>27</v>
       </c>
@@ -6698,11 +6698,11 @@
       <c r="G170" s="60">
         <v>2</v>
       </c>
-      <c r="H170" s="68"/>
-      <c r="I170" s="80"/>
+      <c r="H170" s="76"/>
+      <c r="I170" s="72"/>
       <c r="J170" s="5"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="41">
         <v>28</v>
       </c>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="J171" s="5"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="27"/>
       <c r="B172" s="33"/>
       <c r="C172" s="31"/>
@@ -6742,7 +6742,7 @@
       <c r="I172" s="9"/>
       <c r="J172" s="5"/>
     </row>
-    <row r="173" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
         <v>188</v>
       </c>
@@ -6756,7 +6756,7 @@
       <c r="I173" s="17"/>
       <c r="J173" s="15"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="35">
         <v>1</v>
       </c>
@@ -6776,7 +6776,7 @@
       <c r="G174" s="58">
         <v>1</v>
       </c>
-      <c r="H174" s="71" t="s">
+      <c r="H174" s="79" t="s">
         <v>190</v>
       </c>
       <c r="I174" s="49" t="s">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J174" s="5"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="35">
         <v>2</v>
       </c>
@@ -6804,13 +6804,13 @@
       <c r="G175" s="58">
         <v>1</v>
       </c>
-      <c r="H175" s="71"/>
+      <c r="H175" s="79"/>
       <c r="I175" s="49" t="s">
         <v>504</v>
       </c>
       <c r="J175" s="5"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="35">
         <v>3</v>
       </c>
@@ -6830,13 +6830,13 @@
       <c r="G176" s="58">
         <v>1</v>
       </c>
-      <c r="H176" s="71"/>
+      <c r="H176" s="79"/>
       <c r="I176" s="49" t="s">
         <v>504</v>
       </c>
       <c r="J176" s="5"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="35">
         <v>4</v>
       </c>
@@ -6856,13 +6856,13 @@
       <c r="G177" s="58">
         <v>1</v>
       </c>
-      <c r="H177" s="71"/>
+      <c r="H177" s="79"/>
       <c r="I177" s="49" t="s">
         <v>504</v>
       </c>
       <c r="J177" s="5"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="35">
         <v>5</v>
       </c>
@@ -6882,13 +6882,13 @@
       <c r="G178" s="58">
         <v>1</v>
       </c>
-      <c r="H178" s="71"/>
+      <c r="H178" s="79"/>
       <c r="I178" s="49" t="s">
         <v>504</v>
       </c>
       <c r="J178" s="5"/>
     </row>
-    <row r="179" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="18" t="s">
         <v>193</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="I179" s="17"/>
       <c r="J179" s="15"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>1</v>
       </c>
@@ -6924,7 +6924,7 @@
       <c r="I180" s="9"/>
       <c r="J180" s="5"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>2</v>
       </c>
@@ -6946,7 +6946,7 @@
       <c r="I181" s="9"/>
       <c r="J181" s="5"/>
     </row>
-    <row r="182" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>3</v>
       </c>
@@ -6968,7 +6968,7 @@
       <c r="I182" s="9"/>
       <c r="J182" s="5"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>4</v>
       </c>
@@ -6990,7 +6990,7 @@
       <c r="I183" s="9"/>
       <c r="J183" s="5"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>5</v>
       </c>
@@ -7012,7 +7012,7 @@
       <c r="I184" s="9"/>
       <c r="J184" s="5"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>6</v>
       </c>
@@ -7032,7 +7032,7 @@
       <c r="I185" s="9"/>
       <c r="J185" s="5"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>7</v>
       </c>
@@ -7054,7 +7054,7 @@
       <c r="I186" s="9"/>
       <c r="J186" s="5"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>8</v>
       </c>
@@ -7076,7 +7076,7 @@
       <c r="I187" s="9"/>
       <c r="J187" s="5"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>9</v>
       </c>
@@ -7098,7 +7098,7 @@
       <c r="I188" s="9"/>
       <c r="J188" s="5"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>10</v>
       </c>
@@ -7120,7 +7120,7 @@
       <c r="I189" s="9"/>
       <c r="J189" s="5"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>11</v>
       </c>
@@ -7142,7 +7142,7 @@
       <c r="I190" s="9"/>
       <c r="J190" s="5"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>12</v>
       </c>
@@ -7164,7 +7164,7 @@
       <c r="I191" s="9"/>
       <c r="J191" s="5"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>13</v>
       </c>
@@ -7186,7 +7186,7 @@
       <c r="I192" s="9"/>
       <c r="J192" s="5"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>14</v>
       </c>
@@ -7208,568 +7208,568 @@
       <c r="I193" s="9"/>
       <c r="J193" s="5"/>
     </row>
-    <row r="195" spans="1:10" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A195" s="69" t="s">
+    <row r="195" spans="1:10" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="77" t="s">
         <v>456</v>
       </c>
-      <c r="B195" s="69"/>
-      <c r="C195" s="69"/>
+      <c r="B195" s="77"/>
+      <c r="C195" s="77"/>
       <c r="D195" s="21"/>
-      <c r="E195" s="70" t="s">
+      <c r="E195" s="78" t="s">
         <v>457</v>
       </c>
-      <c r="F195" s="70"/>
-      <c r="G195" s="70"/>
+      <c r="F195" s="78"/>
+      <c r="G195" s="78"/>
       <c r="H195" s="47"/>
       <c r="J195" s="21"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -7779,16 +7779,16 @@
   </sheetData>
   <autoFilter ref="H1:H276" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="A195:C195"/>
+    <mergeCell ref="E195:G195"/>
+    <mergeCell ref="H174:H178"/>
+    <mergeCell ref="H53:H56"/>
     <mergeCell ref="I3:I19"/>
     <mergeCell ref="H4:H18"/>
     <mergeCell ref="I22:I30"/>
     <mergeCell ref="I144:I170"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="H144:H170"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="E195:G195"/>
-    <mergeCell ref="H174:H178"/>
-    <mergeCell ref="H53:H56"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
